--- a/artfynd/A 19052-2024 artfynd.xlsx
+++ b/artfynd/A 19052-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136214765</v>
       </c>
       <c r="B2" t="n">
-        <v>103637</v>
+        <v>103640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19052-2024 artfynd.xlsx
+++ b/artfynd/A 19052-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136214765</v>
       </c>
       <c r="B2" t="n">
-        <v>103640</v>
+        <v>103641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19052-2024 artfynd.xlsx
+++ b/artfynd/A 19052-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136214765</v>
       </c>
       <c r="B2" t="n">
-        <v>103641</v>
+        <v>103646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19052-2024 artfynd.xlsx
+++ b/artfynd/A 19052-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136214765</v>
       </c>
       <c r="B2" t="n">
-        <v>103646</v>
+        <v>103648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
